--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://flotalis-my.sharepoint.com/personal/analistafleet_flotalis_onmicrosoft_com/Documents/Documentos/People/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="8_{3FF9ADBE-D27F-465B-A0B0-0DDC37FB6C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDA8C20C-2AC8-4031-BCBD-30A28470C376}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{3FF9ADBE-D27F-465B-A0B0-0DDC37FB6C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D2C967D-A552-4007-9ED9-849EFCB40E17}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1FA90F1C-6BCA-4B6B-9E30-70BAA3120B5F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="28">
   <si>
     <t xml:space="preserve">Cedula </t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>AUXILIAR DE FLOTA</t>
+  </si>
+  <si>
+    <t>Fecha de Ingreso</t>
   </si>
 </sst>
 </file>
@@ -167,7 +170,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="9">
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -187,16 +211,21 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B47BFD5C-2F0D-46AC-BED7-8AEBACB5E11A}" name="Tabla1" displayName="Tabla1" ref="A1:F14" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:F14" xr:uid="{B47BFD5C-2F0D-46AC-BED7-8AEBACB5E11A}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{08FD95BE-322F-4530-96DE-42379D689E59}" name="Cedula " dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{AA1FB91F-F835-4545-AAB9-4F0338B3B298}" name="Nombre"/>
-    <tableColumn id="3" xr3:uid="{DFA235E0-8238-4195-A9A6-08A77C5099FE}" name="Cargo"/>
-    <tableColumn id="7" xr3:uid="{6250D9A2-F8D6-4BD0-AC2B-D59C82DDECEA}" name="Grupo"/>
-    <tableColumn id="4" xr3:uid="{3A84625C-A2E7-46C5-948F-5F3BF84D7D1B}" name="Region"/>
-    <tableColumn id="5" xr3:uid="{6EB0C740-C336-4E45-AD56-88484301A468}" name="Rol"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B47BFD5C-2F0D-46AC-BED7-8AEBACB5E11A}" name="Tabla1" displayName="Tabla1" ref="A1:G14" totalsRowShown="0" headerRowDxfId="8" dataDxfId="0">
+  <autoFilter ref="A1:G14" xr:uid="{B47BFD5C-2F0D-46AC-BED7-8AEBACB5E11A}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{08FD95BE-322F-4530-96DE-42379D689E59}" name="Cedula " dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{AA1FB91F-F835-4545-AAB9-4F0338B3B298}" name="Nombre" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{DFA235E0-8238-4195-A9A6-08A77C5099FE}" name="Cargo" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{6250D9A2-F8D6-4BD0-AC2B-D59C82DDECEA}" name="Grupo" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{3A84625C-A2E7-46C5-948F-5F3BF84D7D1B}" name="Region" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{020606C6-7FD8-40C7-B673-D20484DBE02C}" name="Rol" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{6EB0C740-C336-4E45-AD56-88484301A468}" name="Fecha de Ingreso" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -519,17 +548,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D24ED-2D17-4380-B03B-2EFF0ECA127F}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="2"/>
     <col min="2" max="2" width="31.88671875" customWidth="1"/>
     <col min="3" max="3" width="33.21875" customWidth="1"/>
     <col min="4" max="4" width="21.77734375" customWidth="1"/>
-    <col min="6" max="6" width="25.88671875" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" customWidth="1"/>
+    <col min="7" max="7" width="25.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -548,266 +578,282 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1193244444</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>79972886</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1130669449</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1082248585</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1107069861</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1110282146</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>1085547172</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>1061203133</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>10386100</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>1114733770</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>2378050</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>16844878</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>1006016305</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>8</v>
-      </c>
+      <c r="D14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
